--- a/tests/Kookerella.CsOpenXmlDsl.Tests/Examples/TextNumberBooleanDateCells/output.xlsx
+++ b/tests/Kookerella.CsOpenXmlDsl.Tests/Examples/TextNumberBooleanDateCells/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R68044acbbb10428f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R0634a2b54ba940e9"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/tests/Kookerella.CsOpenXmlDsl.Tests/Examples/TextNumberBooleanDateCells/output.xlsx
+++ b/tests/Kookerella.CsOpenXmlDsl.Tests/Examples/TextNumberBooleanDateCells/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R0634a2b54ba940e9"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Rfffa8ddd514e45a6"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/tests/Kookerella.CsOpenXmlDsl.Tests/Examples/TextNumberBooleanDateCells/output.xlsx
+++ b/tests/Kookerella.CsOpenXmlDsl.Tests/Examples/TextNumberBooleanDateCells/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Rfffa8ddd514e45a6"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Re2932ac4ef034800"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/tests/Kookerella.CsOpenXmlDsl.Tests/Examples/TextNumberBooleanDateCells/output.xlsx
+++ b/tests/Kookerella.CsOpenXmlDsl.Tests/Examples/TextNumberBooleanDateCells/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Re2932ac4ef034800"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Rd8ec35de3aa04aa8"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/tests/Kookerella.CsOpenXmlDsl.Tests/Examples/TextNumberBooleanDateCells/output.xlsx
+++ b/tests/Kookerella.CsOpenXmlDsl.Tests/Examples/TextNumberBooleanDateCells/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Rd8ec35de3aa04aa8"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Rab9550b1379948ab"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/tests/Kookerella.CsOpenXmlDsl.Tests/Examples/TextNumberBooleanDateCells/output.xlsx
+++ b/tests/Kookerella.CsOpenXmlDsl.Tests/Examples/TextNumberBooleanDateCells/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Rab9550b1379948ab"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R1f43643537974d8e"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/tests/Kookerella.CsOpenXmlDsl.Tests/Examples/TextNumberBooleanDateCells/output.xlsx
+++ b/tests/Kookerella.CsOpenXmlDsl.Tests/Examples/TextNumberBooleanDateCells/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R1f43643537974d8e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R3b60dcb011f74154"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/tests/Kookerella.CsOpenXmlDsl.Tests/Examples/TextNumberBooleanDateCells/output.xlsx
+++ b/tests/Kookerella.CsOpenXmlDsl.Tests/Examples/TextNumberBooleanDateCells/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R3b60dcb011f74154"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R75d29a9ee9ca4c4f"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/tests/Kookerella.CsOpenXmlDsl.Tests/Examples/TextNumberBooleanDateCells/output.xlsx
+++ b/tests/Kookerella.CsOpenXmlDsl.Tests/Examples/TextNumberBooleanDateCells/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R75d29a9ee9ca4c4f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R0d4875410b6b41ca"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/tests/Kookerella.CsOpenXmlDsl.Tests/Examples/TextNumberBooleanDateCells/output.xlsx
+++ b/tests/Kookerella.CsOpenXmlDsl.Tests/Examples/TextNumberBooleanDateCells/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R0d4875410b6b41ca"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Ra4813e36a8154d76"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/tests/Kookerella.CsOpenXmlDsl.Tests/Examples/TextNumberBooleanDateCells/output.xlsx
+++ b/tests/Kookerella.CsOpenXmlDsl.Tests/Examples/TextNumberBooleanDateCells/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Ra4813e36a8154d76"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R508098c16c524d45"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/tests/Kookerella.CsOpenXmlDsl.Tests/Examples/TextNumberBooleanDateCells/output.xlsx
+++ b/tests/Kookerella.CsOpenXmlDsl.Tests/Examples/TextNumberBooleanDateCells/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R508098c16c524d45"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R85642003676d4091"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/tests/Kookerella.CsOpenXmlDsl.Tests/Examples/TextNumberBooleanDateCells/output.xlsx
+++ b/tests/Kookerella.CsOpenXmlDsl.Tests/Examples/TextNumberBooleanDateCells/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R85642003676d4091"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R591b4320f82a4d07"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/tests/Kookerella.CsOpenXmlDsl.Tests/Examples/TextNumberBooleanDateCells/output.xlsx
+++ b/tests/Kookerella.CsOpenXmlDsl.Tests/Examples/TextNumberBooleanDateCells/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R591b4320f82a4d07"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R880660d2cfe34c60"/>
   </x:sheets>
 </x:workbook>
 </file>
